--- a/public/modelli/modello-preventivo-infissi.xlsx
+++ b/public/modelli/modello-preventivo-infissi.xlsx
@@ -666,10 +666,7 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="K3" s="6">
-        <f>TODAY()</f>
-        <v/>
-      </c>
+      <c r="K3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="I4" s="4" t="inlineStr">
